--- a/SpringCloud以及前沿技术/23_EasyExcel/工作簿WriteDemo1.xlsx
+++ b/SpringCloud以及前沿技术/23_EasyExcel/工作簿WriteDemo1.xlsx
@@ -103,17 +103,17 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>字符串1692196448412</t>
+          <t>字符串1692243324159</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>数字1692196448413</t>
+          <t>数字1692243324162</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>日期1692196448413</t>
+          <t>日期1692243324162</t>
         </is>
       </c>
     </row>
@@ -124,7 +124,7 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45154.94037797453</v>
+        <v>45155.48292231481</v>
       </c>
       <c r="C2" t="n">
         <v>0.56</v>
@@ -137,7 +137,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45154.94037797453</v>
+        <v>45155.48292231481</v>
       </c>
       <c r="C3" t="n">
         <v>0.56</v>
@@ -150,7 +150,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45154.94037797453</v>
+        <v>45155.48292231481</v>
       </c>
       <c r="C4" t="n">
         <v>0.56</v>
@@ -163,7 +163,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45154.94037797453</v>
+        <v>45155.48292231481</v>
       </c>
       <c r="C5" t="n">
         <v>0.56</v>
@@ -176,7 +176,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45154.94037797453</v>
+        <v>45155.48292231481</v>
       </c>
       <c r="C6" t="n">
         <v>0.56</v>
@@ -189,7 +189,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45154.94037797453</v>
+        <v>45155.48292231481</v>
       </c>
       <c r="C7" t="n">
         <v>0.56</v>
@@ -202,7 +202,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45154.94037797453</v>
+        <v>45155.48292231481</v>
       </c>
       <c r="C8" t="n">
         <v>0.56</v>
@@ -215,7 +215,7 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45154.94037797453</v>
+        <v>45155.48292231481</v>
       </c>
       <c r="C9" t="n">
         <v>0.56</v>
@@ -228,7 +228,7 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45154.94037797453</v>
+        <v>45155.48292231481</v>
       </c>
       <c r="C10" t="n">
         <v>0.56</v>
@@ -241,7 +241,7 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45154.94037797453</v>
+        <v>45155.48292231481</v>
       </c>
       <c r="C11" t="n">
         <v>0.56</v>
